--- a/Aii竞彩推荐_2026-05-16.xlsx
+++ b/Aii竞彩推荐_2026-05-16.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞彩推荐总表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每场分析" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="串关方案" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="竞彩推荐总表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="每场分析" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="串关方案" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,6 +59,17 @@
       <b val="1"/>
       <color rgb="001A3C6E"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00006600"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00006600"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="7">
@@ -164,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -206,6 +217,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,9 +685,9 @@
           <t>客队形势</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>关键看点</t>
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>SP数据/让球/欧洲赔率</t>
         </is>
       </c>
     </row>
@@ -709,9 +732,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>SP2.70/3.50/2.12 让球-1</t>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>SP2.70/3.50/2.12 让球-1 | 欧赔2.07/4.27/2.95</t>
         </is>
       </c>
     </row>
@@ -1085,9 +1108,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>SP0.00/0.00/0.00 让球0</t>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>SP0.00/0.00/0.00 让球0 | 欧赔1.79/3.81/4.64</t>
         </is>
       </c>
     </row>
@@ -1132,9 +1155,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>SP0.00/0.00/0.00 让球0</t>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>SP0.00/0.00/0.00 让球0 | 欧赔1.36/5.8/7.0</t>
         </is>
       </c>
     </row>
@@ -1226,9 +1249,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>SP5.90/4.00/1.41 让球-1</t>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>SP5.90/4.00/1.41 让球-1 | 欧赔1.6/4.75/5.25</t>
         </is>
       </c>
     </row>
@@ -1273,9 +1296,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>SP5.00/3.75/1.51 让球-1</t>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>SP5.00/3.75/1.51 让球-1 | 欧赔2.2/4.2/3.0</t>
         </is>
       </c>
     </row>
@@ -3294,9 +3317,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I64" s="7" t="inlineStr">
-        <is>
-          <t>SP2.75/3.15/2.23 让球+1</t>
+      <c r="I64" s="21" t="inlineStr">
+        <is>
+          <t>SP2.75/3.15/2.23 让球+1 | 欧赔3.06/3.23/2.52</t>
         </is>
       </c>
     </row>
@@ -3717,9 +3740,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>SP1.16/6.70/8.50 让球-2</t>
+      <c r="I73" s="20" t="inlineStr">
+        <is>
+          <t>SP1.16/6.70/8.50 让球-2 | 欧赔1.23/6.75/8.0</t>
         </is>
       </c>
     </row>
@@ -3764,9 +3787,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I74" s="7" t="inlineStr">
-        <is>
-          <t>SP1.73/4.70/2.95 让球-2</t>
+      <c r="I74" s="21" t="inlineStr">
+        <is>
+          <t>SP1.73/4.70/2.95 让球-2 | 欧赔1.13/9.0/11.0</t>
         </is>
       </c>
     </row>
@@ -3811,9 +3834,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>SP1.78/4.00/3.15 让球-1</t>
+      <c r="I75" s="20" t="inlineStr">
+        <is>
+          <t>SP1.78/4.00/3.15 让球-1 | 欧赔1.92/4.25/3.35</t>
         </is>
       </c>
     </row>
@@ -3905,9 +3928,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>SP2.48/3.90/2.13 让球+1</t>
+      <c r="I77" s="20" t="inlineStr">
+        <is>
+          <t>SP2.48/3.90/2.13 让球+1 | 欧赔2.45/3.9/2.35</t>
         </is>
       </c>
     </row>
@@ -3952,9 +3975,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I78" s="7" t="inlineStr">
-        <is>
-          <t>SP3.13/4.25/1.74 让球+1</t>
+      <c r="I78" s="21" t="inlineStr">
+        <is>
+          <t>SP3.13/4.25/1.74 让球+1 | 欧赔3.35/4.45/1.9</t>
         </is>
       </c>
     </row>
@@ -3999,9 +4022,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I79" s="6" t="inlineStr">
-        <is>
-          <t>SP3.15/4.00/1.78 让球+1</t>
+      <c r="I79" s="20" t="inlineStr">
+        <is>
+          <t>SP3.15/4.00/1.78 让球+1 | 欧赔3.25/3.95/2.02</t>
         </is>
       </c>
     </row>
@@ -4046,9 +4069,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>SP4.10/4.56/1.50 让球+1</t>
+      <c r="I80" s="21" t="inlineStr">
+        <is>
+          <t>SP4.10/4.56/1.50 让球+1 | 欧赔4.1/4.6/1.58</t>
         </is>
       </c>
     </row>
@@ -4093,9 +4116,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>SP2.80/3.85/1.95 让球+1</t>
+      <c r="I81" s="20" t="inlineStr">
+        <is>
+          <t>SP2.80/3.85/1.95 让球+1 | 欧赔2.62/3.95/2.42</t>
         </is>
       </c>
     </row>
@@ -4328,9 +4351,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I86" s="7" t="inlineStr">
-        <is>
-          <t>SP1.53/3.80/4.70 让球-1</t>
+      <c r="I86" s="21" t="inlineStr">
+        <is>
+          <t>SP1.53/3.80/4.70 让球-1 | 欧赔1.68/4.14/4.75</t>
         </is>
       </c>
     </row>
@@ -4375,9 +4398,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>SP1.27/4.55/8.20 让球-1</t>
+      <c r="I87" s="20" t="inlineStr">
+        <is>
+          <t>SP1.27/4.55/8.20 让球-1 | 欧赔1.09/7.0/14.0</t>
         </is>
       </c>
     </row>
@@ -4469,9 +4492,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>SP2.45/3.90/2.15 让球-2</t>
+      <c r="I89" s="20" t="inlineStr">
+        <is>
+          <t>SP2.45/3.90/2.15 让球-2 | 欧赔1.21/6.67/12.47</t>
         </is>
       </c>
     </row>
@@ -4516,9 +4539,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I90" s="7" t="inlineStr">
-        <is>
-          <t>SP9.50/5.70/1.18 让球+2</t>
+      <c r="I90" s="21" t="inlineStr">
+        <is>
+          <t>SP9.50/5.70/1.18 让球+2 | 欧赔8.93/6.03/1.29</t>
         </is>
       </c>
     </row>
@@ -4939,9 +4962,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I99" s="6" t="inlineStr">
-        <is>
-          <t>SP0.00/0.00/0.00 让球0</t>
+      <c r="I99" s="20" t="inlineStr">
+        <is>
+          <t>SP0.00/0.00/0.00 让球0 | 欧赔1.53/4.47/6.29</t>
         </is>
       </c>
     </row>
@@ -5033,9 +5056,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I101" s="6" t="inlineStr">
-        <is>
-          <t>SP1.48/4.10/4.80 让球-1</t>
+      <c r="I101" s="20" t="inlineStr">
+        <is>
+          <t>SP1.48/4.10/4.80 让球-1 | 欧赔1.67/4.35/4.84</t>
         </is>
       </c>
     </row>
@@ -5268,9 +5291,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I106" s="7" t="inlineStr">
-        <is>
-          <t>SP3.66/3.55/1.74 让球+1</t>
+      <c r="I106" s="21" t="inlineStr">
+        <is>
+          <t>SP3.66/3.55/1.74 让球+1 | 欧赔3.75/3.96/1.94</t>
         </is>
       </c>
     </row>
@@ -5315,9 +5338,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I107" s="6" t="inlineStr">
-        <is>
-          <t>SP1.73/3.37/3.95 让球-1</t>
+      <c r="I107" s="20" t="inlineStr">
+        <is>
+          <t>SP1.73/3.37/3.95 让球-1 | 欧赔1.83/3.92/4.26</t>
         </is>
       </c>
     </row>
@@ -5362,12 +5385,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I108" s="7" t="inlineStr">
-        <is>
-          <t>SP1.54/3.85/4.55 让球-1</t>
-        </is>
-      </c>
-    </row>
+      <c r="I108" s="21" t="inlineStr">
+        <is>
+          <t>SP1.54/3.85/4.55 让球-1 | 欧赔1.67/4.42/4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
@@ -10027,6 +10054,9 @@
         </is>
       </c>
     </row>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="217"/>
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
@@ -15286,6 +15316,9 @@
         </is>
       </c>
     </row>
+    <row r="320"/>
+    <row r="321"/>
+    <row r="322"/>
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
@@ -15542,9 +15575,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I328" s="6" t="inlineStr">
-        <is>
-          <t>P主=35%P平=24%P客=40%</t>
+      <c r="I328" s="20" t="inlineStr">
+        <is>
+          <t>P主=35%P平=24%P客=40% | 欧赔3.35/4.45/1.9</t>
         </is>
       </c>
       <c r="J328" s="6" t="inlineStr">
@@ -15594,9 +15627,9 @@
           <t>★胆</t>
         </is>
       </c>
-      <c r="I329" s="11" t="inlineStr">
-        <is>
-          <t>P主=46% 优势15%</t>
+      <c r="I329" s="22" t="inlineStr">
+        <is>
+          <t>P主=46% 优势15% | 欧赔1.92/4.25/3.35</t>
         </is>
       </c>
       <c r="J329" s="11" t="inlineStr">
@@ -15646,9 +15679,9 @@
           <t>★胆</t>
         </is>
       </c>
-      <c r="I330" s="11" t="inlineStr">
-        <is>
-          <t>P主=55% 优势31%</t>
+      <c r="I330" s="22" t="inlineStr">
+        <is>
+          <t>P主=55% 优势31% | 欧赔1.23/6.75/8.0</t>
         </is>
       </c>
       <c r="J330" s="11" t="inlineStr">
@@ -15750,9 +15783,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I332" s="6" t="inlineStr">
-        <is>
-          <t>P主=43%</t>
+      <c r="I332" s="20" t="inlineStr">
+        <is>
+          <t>P主=43% | 欧赔2.88/3.55/2.38</t>
         </is>
       </c>
       <c r="J332" s="6" t="inlineStr">
@@ -15802,9 +15835,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I333" s="6" t="inlineStr">
-        <is>
-          <t>P主=39%P平=25%P客=36%</t>
+      <c r="I333" s="20" t="inlineStr">
+        <is>
+          <t>P主=39%P平=25%P客=36% | 欧赔2.45/3.9/2.35</t>
         </is>
       </c>
       <c r="J333" s="6" t="inlineStr">
@@ -15906,9 +15939,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I335" s="6" t="inlineStr">
-        <is>
-          <t>P主=53% 优势28%</t>
+      <c r="I335" s="20" t="inlineStr">
+        <is>
+          <t>P主=53% 优势28% | 欧赔1.68/4.14/4.75</t>
         </is>
       </c>
       <c r="J335" s="6" t="inlineStr">
@@ -16073,6 +16106,8 @@
         </is>
       </c>
     </row>
+    <row r="339"/>
+    <row r="340"/>
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
@@ -16143,6 +16178,9 @@
         </is>
       </c>
     </row>
+    <row r="351"/>
+    <row r="352"/>
+    <row r="353"/>
     <row r="354">
       <c r="A354" s="5" t="inlineStr">
         <is>
@@ -16370,6 +16408,9 @@
         </is>
       </c>
     </row>
+    <row r="360"/>
+    <row r="361"/>
+    <row r="362"/>
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
